--- a/stories/arbres/TREE-JEU-031.xlsx
+++ b/stories/arbres/TREE-JEU-031.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Adam est avec maman, près de la fenêtre. Adam a envie de jouer. maman est là, tout près. On va apprendre : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam écoute maman. Adam entend les mots : but, passer, espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Adam se souvient : but, passer, espace montré. Voici le geste : passer ; tirer au but dans l'espace. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Adam se souvient : but, passer, espace montré. Voici le geste : passer ; tirer au but dans l'espace. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Adam se souvient : but, passer, espace montré. Voici le geste : passer ; tirer au but dans l'espace. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Petit jeu de foot.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : passer ; tirer au but dans l'espace. Adam respire. Adam retient : but, passer, espace montré. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Adam se souvient : but, passer, espace montré. Voici le geste : passer ; tirer au but dans l'espace. On écoute jusqu'au bout. maman dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Adam se souvient : but, passer, espace montré. Voici le geste : passer ; tirer au but dans l'espace. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Adam se souvient : but, passer, espace montré. Voici le geste : passer ; tirer au but dans l'espace. On écoute jusqu'au bout.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Petit jeu de foot.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : passer ; tirer au but dans l'espace. Adam respire. Adam retient : but, passer, espace montré. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. La lumière est claire. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Adam se souvient : but, passer, espace montré. Voici le geste : passer ; tirer au but dans l'espace. On attend son tour. maman dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Adam se souvient : but, passer, espace montré. Voici le geste : passer ; tirer au but dans l'espace. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Adam se souvient : but, passer, espace montré. Voici le geste : passer ; tirer au but dans l'espace. On attend son tour.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Petit jeu de foot.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : passer ; tirer au but dans l'espace. Adam respire. Adam retient : but, passer, espace montré. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-JEU-031.xlsx
+++ b/stories/arbres/TREE-JEU-031.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Adam est avec maman, près de la fenêtre. Adam a envie de jouer. maman est là, tout près. On va apprendre : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam écoute maman. Adam entend les mots : but, passer, espace montré.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Petit jeu de foot.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : passer ; tirer au but dans l'espace. Adam respire. Adam retient : but, passer, espace montré. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Adam a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Adam rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Adam rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Adam rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Adam a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Adam rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Adam rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Adam rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Adam a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Adam rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Petit jeu de foot.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : passer ; tirer au but dans l'espace. Adam respire. Adam retient : but, passer, espace montré. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Adam a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Adam rejoint Tom. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Adam rejoint Léa. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Adam rejoint Sami. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Adam a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Adam rejoint Léa. La lumière est claire. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Adam a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Adam rejoint Tom. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Adam rejoint Léa. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Adam rejoint Sami. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Que fait-on ? Petit jeu de foot.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Voici le geste : passer ; tirer au but dans l'espace. Adam respire. Adam retient : but, passer, espace montré. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Adam a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Adam rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Adam a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Adam rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Adam rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Adam rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Adam a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : passer ; tirer au but dans l'espace. Adam répète tout bas : but, passer, espace montré. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Adam rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Tom. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Adam rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Léa. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Adam rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Sami. Adam a appris : Petit jeu de foot. Voici le geste : passer ; tirer au but dans l'espace. Adam a entendu : but, passer, espace montré. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
